--- a/Figure 6/Figure 6-Q.xlsx
+++ b/Figure 6/Figure 6-Q.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2568CC33-5012-4B52-AE50-872D8D2C9BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E918FB-A22B-4A30-9E46-A752D8EB5452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-1540" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,9 +107,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -127,10 +124,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -153,10 +149,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -444,194 +439,201 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>1.7150487171855846</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>0.89160977421903964</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>0.54798252365678335</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>1.314070347506771</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>2.3318926751285529</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="1">
+        <v>0.84</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>1.3103894926188535</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="1">
+        <v>1.52</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1">
-        <v>0.43899597004316149</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1">
-        <v>0.17448055020537204</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="1">
-        <v>9.2535703942936906E-2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>0.27282633555255081</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1">
-        <v>0.27625615248251573</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="1">
-        <v>0.38526967663748701</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1">
-        <v>0.29898119851339905</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="1">
-        <v>0.19561037783125329</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="1">
-        <v>0.32926686451002196</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="1">
-        <v>0.2096926565138145</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2"/>
+      <c r="B20" s="1">
+        <v>1.54</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="1">
-        <v>0.2294227188325586</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="1">
-        <v>0.18731988960093979</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="1">
-        <v>0.24769404574632403</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="1">
-        <v>0.14689382418663188</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="1">
-        <v>0.56340011508171384</v>
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
